--- a/artfynd/A 8349-2024 artfynd.xlsx
+++ b/artfynd/A 8349-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,6 +1015,120 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115125865</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57255</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Digerberget SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500639</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6595421</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8349-2024 artfynd.xlsx
+++ b/artfynd/A 8349-2024 artfynd.xlsx
@@ -1020,11 +1020,11 @@
         <v>115125865</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/artfynd/A 8349-2024 artfynd.xlsx
+++ b/artfynd/A 8349-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>115125865</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 8349-2024 artfynd.xlsx
+++ b/artfynd/A 8349-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>115125865</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 8349-2024 artfynd.xlsx
+++ b/artfynd/A 8349-2024 artfynd.xlsx
@@ -1035,11 +1035,6 @@
       <c r="E5" t="n">
         <v>100049</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 8349-2024 artfynd.xlsx
+++ b/artfynd/A 8349-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>115125865</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,6 +1034,11 @@
       </c>
       <c r="E5" t="n">
         <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
